--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,42 +1893,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1962,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,39 +2002,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46064</v>
+        <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44998</v>
+        <v>45119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45119</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46085</v>
+        <v>46064</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,13 +2468,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2517,7 +2512,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2531,10 +2526,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46106</v>
+        <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2552,7 +2547,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2595,7 +2590,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2609,10 +2604,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2624,8 +2619,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2685,7 +2685,7 @@
         <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45854</v>
+        <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45155</v>
+        <v>45854</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>20.9</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44791</v>
+        <v>45155</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>20.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>46185</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3123,7 +3123,7 @@
         <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3208,8 +3208,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3252,7 +3257,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3271,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3281,8 +3286,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3335,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3339,10 +3349,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46273</v>
+        <v>44791</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3354,13 +3364,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3408,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3417,10 +3422,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3432,13 +3437,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,46 +1893,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,16 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2002,35 +1998,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44998</v>
+        <v>44791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45119</v>
+        <v>45327</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,8 +2395,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2439,7 +2444,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2458,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,8 +2473,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2512,7 +2522,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2526,10 +2536,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46085</v>
+        <v>46111</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,13 +2551,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2590,7 +2595,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2604,10 +2609,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2619,13 +2624,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46111</v>
+        <v>44517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45854</v>
+        <v>44998</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45155</v>
+        <v>45119</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>20.9</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2977,7 +2977,7 @@
         <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46185</v>
+        <v>46064</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44517</v>
+        <v>46185</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46273</v>
+        <v>45155</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3208,13 +3208,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>20.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3257,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3271,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3286,13 +3281,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3335,7 +3325,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3349,10 +3339,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44791</v>
+        <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3364,8 +3354,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3408,7 +3403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3422,10 +3417,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3437,8 +3432,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,42 +1893,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1962,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,39 +2002,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44791</v>
+        <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45327</v>
+        <v>45119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46085</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,13 +2395,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2444,7 +2439,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2458,10 +2453,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46106</v>
+        <v>46064</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2473,13 +2468,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2522,7 +2512,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2536,10 +2526,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46111</v>
+        <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2551,8 +2541,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2595,7 +2590,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2609,10 +2604,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2625,7 +2620,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>20.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2668,7 +2663,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2682,10 +2677,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45854</v>
+        <v>46106</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2697,8 +2692,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44517</v>
+        <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44998</v>
+        <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45119</v>
+        <v>44998</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44998</v>
+        <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46064</v>
+        <v>45854</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46185</v>
+        <v>44791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>20.9</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44998</v>
+        <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3342,7 +3342,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3420,7 +3420,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,46 +1893,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,16 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2002,35 +1998,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44998</v>
+        <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45119</v>
+        <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,8 +2322,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2371,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2385,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2396,7 +2401,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2439,7 +2444,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2458,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,8 +2473,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2512,7 +2522,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2526,10 +2536,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46085</v>
+        <v>46111</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,13 +2551,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2590,7 +2595,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2604,10 +2609,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45155</v>
+        <v>46111</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2620,7 +2625,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>20.9</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2663,7 +2668,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2677,10 +2682,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46106</v>
+        <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2692,13 +2697,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>20.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44998</v>
+        <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44517</v>
+        <v>44791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45854</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44791</v>
+        <v>46273</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3135,8 +3135,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3184,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3198,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3208,8 +3213,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3252,7 +3262,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3276,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46185</v>
+        <v>44517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3292,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3335,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3339,10 +3349,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3354,13 +3364,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3408,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3417,10 +3422,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3432,13 +3437,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45853</v>
+        <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46064</v>
+        <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46085</v>
+        <v>45327</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,13 +2322,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2371,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2385,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44998</v>
+        <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2401,7 +2396,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2444,7 +2439,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2458,10 +2453,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46106</v>
+        <v>45854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2473,13 +2468,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2522,7 +2512,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2536,10 +2526,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2552,7 +2542,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>20.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2595,7 +2585,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2609,10 +2599,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46111</v>
+        <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2625,7 +2615,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2668,7 +2658,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2682,10 +2672,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45119</v>
+        <v>44517</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2698,7 +2688,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2731,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2755,10 +2745,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45854</v>
+        <v>44791</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2761,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2814,7 +2804,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2828,10 +2818,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2844,7 +2834,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>20.9</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2887,7 +2877,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2891,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46185</v>
+        <v>46064</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2917,7 +2907,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2950,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +2964,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44791</v>
+        <v>46185</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3033,7 +3023,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3037,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>46085</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3062,8 +3052,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3101,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3115,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46273</v>
+        <v>46106</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3137,7 +3132,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3184,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3198,10 +3193,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46273</v>
+        <v>46111</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3213,13 +3208,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3262,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3276,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44517</v>
+        <v>46111</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3292,7 +3282,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3335,7 +3325,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3349,10 +3339,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3364,8 +3354,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3408,7 +3403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3422,10 +3417,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3437,8 +3432,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44522</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45853</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45327</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45155</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>44517</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44791</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44998</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>46064</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>46185</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46085</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>46106</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>46111</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>46111</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45155</v>
+        <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 67005-2021</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>44522</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>1.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,42 +1893,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1962,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,39 +2002,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45327</v>
+        <v>45119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45119</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>45854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45155</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>44517</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44791</v>
+        <v>46185</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44998</v>
+        <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2877,7 +2877,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46064</v>
+        <v>46085</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,8 +2906,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2950,7 +2955,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46185</v>
+        <v>44791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3023,7 +3028,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3037,10 +3042,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3058,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3101,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3115,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3130,13 +3135,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3196,7 +3196,7 @@
         <v>46111</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46111</v>
+        <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45853</v>
+        <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,46 +1893,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,16 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2002,35 +1998,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44998</v>
+        <v>45155</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>20.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45119</v>
+        <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45854</v>
+        <v>44791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45155</v>
+        <v>45327</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>20.9</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44998</v>
+        <v>46064</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>44517</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46185</v>
+        <v>46085</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,8 +2760,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2804,7 +2809,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2818,10 +2823,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46064</v>
+        <v>44998</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2834,7 +2839,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2877,7 +2882,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2891,10 +2896,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2912,7 +2917,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2955,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44791</v>
+        <v>46111</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2985,7 +2990,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3028,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3042,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3057,13 +3062,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46111</v>
+        <v>44998</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44998</v>
+        <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3342,7 +3342,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3420,7 +3420,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45155</v>
+        <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 67005-2021</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>44522</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>1.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,42 +1893,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1962,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,39 +2002,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>20.9</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44998</v>
+        <v>45119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45119</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44791</v>
+        <v>45155</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>20.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45327</v>
+        <v>45854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46064</v>
+        <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>44517</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46085</v>
+        <v>46064</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,13 +2760,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2809,7 +2804,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2823,10 +2818,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44998</v>
+        <v>46085</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2838,8 +2833,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46106</v>
+        <v>44791</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2911,13 +2911,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2955,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +2969,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46111</v>
+        <v>46185</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2990,7 +2985,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3028,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3042,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3062,8 +3057,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3123,7 +3123,7 @@
         <v>44998</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45854</v>
+        <v>46111</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46185</v>
+        <v>46111</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3342,7 +3342,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3420,7 +3420,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45853</v>
+        <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,46 +1893,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,16 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2002,35 +1998,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44998</v>
+        <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45119</v>
+        <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,8 +2322,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2371,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2385,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>46106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,8 +2400,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2439,7 +2449,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2463,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45155</v>
+        <v>46111</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2469,7 +2479,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>20.9</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2512,7 +2522,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2526,10 +2536,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45854</v>
+        <v>46111</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2542,7 +2552,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2602,7 +2612,7 @@
         <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2658,7 +2668,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2672,10 +2682,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44517</v>
+        <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2688,7 +2698,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2731,7 +2741,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2745,10 +2755,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46064</v>
+        <v>45854</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2761,7 +2771,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2804,7 +2814,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2818,10 +2828,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46085</v>
+        <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,13 +2843,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>20.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2882,7 +2887,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2896,10 +2901,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44791</v>
+        <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2955,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46185</v>
+        <v>44791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3028,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3042,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46106</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3057,13 +3062,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3135,8 +3135,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3184,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3198,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46111</v>
+        <v>46273</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3208,8 +3213,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3252,7 +3262,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3276,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46111</v>
+        <v>44517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3292,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3335,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3339,10 +3349,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3354,13 +3364,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3408,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3417,10 +3422,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3432,13 +3437,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44522</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45853</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46111</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>46111</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45854</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>46273</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>46273</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44998</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44522</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45853</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46111</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>46111</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45854</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>46273</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>46273</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44998</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45155</v>
+        <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 67005-2021</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>44522</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>1.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,42 +1893,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1962,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,39 +2002,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46064</v>
+        <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46085</v>
+        <v>45119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,13 +2322,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2371,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2385,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46106</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2400,13 +2395,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2449,7 +2439,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2463,10 +2453,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46111</v>
+        <v>46064</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2479,7 +2469,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2522,7 +2512,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2536,10 +2526,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46111</v>
+        <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2551,8 +2541,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2595,7 +2590,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2609,10 +2604,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44998</v>
+        <v>45155</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2625,7 +2620,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>20.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2668,7 +2663,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2682,10 +2677,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45119</v>
+        <v>46106</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2697,8 +2692,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45854</v>
+        <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45155</v>
+        <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>20.9</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44791</v>
+        <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>45854</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46273</v>
+        <v>44791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3135,13 +3135,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3184,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3198,10 +3193,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3213,13 +3208,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3262,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3276,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44517</v>
+        <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3292,7 +3282,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3335,7 +3325,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3349,10 +3339,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3364,8 +3354,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3408,7 +3403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3422,10 +3417,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3437,8 +3432,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,46 +1893,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,16 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2002,35 +1998,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2237,7 +2237,7 @@
         <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45119</v>
+        <v>46064</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46064</v>
+        <v>46085</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,8 +2468,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2512,7 +2517,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2526,10 +2531,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2547,7 +2552,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2590,7 +2595,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2604,10 +2609,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45155</v>
+        <v>46111</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2620,7 +2625,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>20.9</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2663,7 +2668,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2677,10 +2682,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2692,13 +2697,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>20.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44998</v>
+        <v>44791</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44517</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45854</v>
+        <v>46185</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44791</v>
+        <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3196,7 +3196,7 @@
         <v>44998</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3342,7 +3342,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3420,7 +3420,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 67005-2021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45853</v>
+        <v>44522</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,22 +1307,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,42 +1893,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1962,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,39 +2002,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2237,7 +2237,7 @@
         <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46064</v>
+        <v>44791</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46085</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,13 +2468,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2517,7 +2512,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2531,10 +2526,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46106</v>
+        <v>44998</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2546,13 +2541,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2595,7 +2585,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2609,10 +2599,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2625,7 +2615,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>20.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2668,7 +2658,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2682,10 +2672,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46111</v>
+        <v>44998</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2698,7 +2688,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2731,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2755,10 +2745,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45854</v>
+        <v>44517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2761,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2814,7 +2804,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2828,10 +2818,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45155</v>
+        <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2844,7 +2834,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>20.9</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2887,7 +2877,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2891,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44791</v>
+        <v>46085</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2916,8 +2906,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2955,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +2969,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>46106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2989,8 +2984,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46185</v>
+        <v>46111</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44517</v>
+        <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44998</v>
+        <v>45854</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44998</v>
+        <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3342,7 +3342,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3420,7 +3420,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 67005-2021</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44522</v>
+        <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,22 +1307,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,46 +1893,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,16 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2002,35 +1998,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44998</v>
+        <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44791</v>
+        <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,8 +2322,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2366,7 +2371,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2385,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45119</v>
+        <v>46106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,8 +2400,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2439,7 +2449,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2463,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45327</v>
+        <v>46111</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2469,7 +2479,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2512,7 +2522,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2526,10 +2536,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44998</v>
+        <v>46111</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2542,7 +2552,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2585,7 +2595,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2599,10 +2609,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2615,7 +2625,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>20.9</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2658,7 +2668,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2672,10 +2682,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44998</v>
+        <v>45854</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2688,7 +2698,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2731,7 +2741,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2745,10 +2755,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44517</v>
+        <v>45119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2761,7 +2771,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2804,7 +2814,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2818,10 +2828,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46064</v>
+        <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2834,7 +2844,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>20.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2877,7 +2887,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2891,10 +2901,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46085</v>
+        <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,13 +2916,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2955,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46106</v>
+        <v>44791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2984,13 +2989,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46111</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46111</v>
+        <v>46273</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3135,8 +3135,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3184,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3198,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45854</v>
+        <v>46273</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3208,8 +3213,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3252,7 +3262,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3276,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46185</v>
+        <v>44517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3292,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3335,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3339,10 +3349,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3354,13 +3364,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3408,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3417,10 +3422,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3432,13 +3437,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45853</v>
+        <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,168 +1331,168 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,42 +1893,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1962,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,39 +2002,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46064</v>
+        <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46085</v>
+        <v>45119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,13 +2322,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2371,7 +2366,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2385,10 +2380,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46106</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2400,13 +2395,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2449,7 +2439,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2463,10 +2453,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46111</v>
+        <v>46064</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2479,7 +2469,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2522,7 +2512,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2536,10 +2526,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46111</v>
+        <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2551,8 +2541,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2595,7 +2590,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2609,10 +2604,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44998</v>
+        <v>46106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2624,8 +2619,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45854</v>
+        <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45119</v>
+        <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2831,7 +2831,7 @@
         <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46185</v>
+        <v>45854</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44791</v>
+        <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>44517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46273</v>
+        <v>46185</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3135,13 +3135,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3184,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3198,10 +3193,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46273</v>
+        <v>44791</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3213,13 +3208,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3262,7 +3252,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3276,10 +3266,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44517</v>
+        <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3292,7 +3282,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3335,7 +3325,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3349,10 +3339,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3364,8 +3354,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3408,7 +3403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3422,10 +3417,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3437,8 +3432,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45211</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44473</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>46064</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>46106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>45854</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>46185</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44791</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2037,24 +2037,24 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S 3579-2023</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45211</v>
+        <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2068,11 +2068,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2081,13 +2081,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2099,72 +2099,76 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/S 3579-2023 artfynd.xlsx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37080-2026 artfynd.xlsx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/S 3579-2023 karta.png", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37080-2026 karta.png", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/S 3579-2023 georefererad karta.tif", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37080-2026 georefererad karta.tif", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/S 3579-2023 FSC-klagomål.docx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37080-2026 FSC-klagomål.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/S 3579-2023 FSC-klagomål mail.docx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37080-2026 FSC-klagomål mail.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/S 3579-2023 tillsynsbegäran.docx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37080-2026 tillsynsbegäran.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/S 3579-2023 tillsynsbegäran mail.docx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37080-2026 tillsynsbegäran mail.docx", "A 37080-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37080-2026 prioriterade fågelarter.docx", "A 37080-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54890-2021</t>
+          <t>S 3579-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44473</v>
+        <v>45211</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,11 +2180,16 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2192,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2201,26 +2210,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/S 3579-2023 artfynd.xlsx", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/S 3579-2023 karta.png", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/S 3579-2023 georefererad karta.tif", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/S 3579-2023 FSC-klagomål.docx", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/S 3579-2023 FSC-klagomål mail.docx", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/S 3579-2023 tillsynsbegäran.docx", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/S 3579-2023 tillsynsbegäran mail.docx", "S 3579-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 54890-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2234,10 +2275,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44998</v>
+        <v>44473</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2250,7 +2291,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2293,7 +2334,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2307,10 +2348,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45119</v>
+        <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2366,7 +2407,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2380,10 +2421,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2396,7 +2437,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2439,7 +2480,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2453,10 +2494,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46064</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2469,7 +2510,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2512,7 +2553,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2526,10 +2567,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46085</v>
+        <v>46064</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,13 +2582,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2590,7 +2626,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2604,10 +2640,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46106</v>
+        <v>46085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2625,7 +2661,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2668,7 +2704,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2682,10 +2718,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2697,8 +2733,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2741,7 +2782,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2758,7 +2799,7 @@
         <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2771,7 +2812,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2814,7 +2855,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2828,10 +2869,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45155</v>
+        <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2844,7 +2885,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>20.9</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2887,7 +2928,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2901,10 +2942,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45854</v>
+        <v>45155</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2917,7 +2958,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>20.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2960,7 +3001,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2974,10 +3015,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44998</v>
+        <v>45854</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2990,7 +3031,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3033,7 +3074,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3047,10 +3088,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44517</v>
+        <v>44998</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3063,7 +3104,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3106,7 +3147,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3120,10 +3161,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46185</v>
+        <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3136,7 +3177,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3220,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3234,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44791</v>
+        <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3252,7 +3293,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3266,10 +3307,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44998</v>
+        <v>44791</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3282,7 +3323,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3366,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3339,10 +3380,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3354,13 +3395,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3439,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3420,7 +3456,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3438,7 +3474,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE33"/>
+  <dimension ref="A1:AE32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45155</v>
+        <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,168 +1331,168 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,46 +1893,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,16 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2002,35 +1998,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45211</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54890-2021</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44473</v>
+        <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44998</v>
+        <v>46064</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45327</v>
+        <v>46085</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2509,8 +2509,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2553,7 +2558,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2567,10 +2572,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2582,8 +2587,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2626,7 +2636,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2640,10 +2650,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46085</v>
+        <v>46111</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2655,13 +2665,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2704,7 +2709,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2718,10 +2723,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2733,13 +2738,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>20.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45155</v>
+        <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>20.9</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45854</v>
+        <v>44791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44998</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44791</v>
+        <v>46273</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3322,8 +3322,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3363,10 +3368,10 @@
       </c>
       <c r="V31" s="2" t="inlineStr"/>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3383,7 +3388,7 @@
         <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3396,7 +3401,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3435,84 +3440,6 @@
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 36934-2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,42 +1893,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1962,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,39 +2002,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45211</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2278,7 +2278,7 @@
         <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46064</v>
+        <v>45119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45119</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46085</v>
+        <v>46064</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2509,13 +2509,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2558,7 +2553,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2572,10 +2567,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46106</v>
+        <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2593,7 +2588,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2636,7 +2631,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2650,10 +2645,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2665,8 +2660,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2726,7 +2726,7 @@
         <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45854</v>
+        <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45155</v>
+        <v>45854</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>20.9</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44791</v>
+        <v>45155</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>20.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>44998</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3249,8 +3249,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3293,7 +3298,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3307,10 +3312,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46273</v>
+        <v>44791</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3322,13 +3327,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,7 +3388,7 @@
         <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45853</v>
+        <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,46 +1893,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,16 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2002,35 +1998,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45211</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44998</v>
+        <v>45155</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>20.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45119</v>
+        <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46064</v>
+        <v>44791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46085</v>
+        <v>45327</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2582,13 +2582,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2631,7 +2626,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2645,10 +2640,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46106</v>
+        <v>46185</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2660,13 +2655,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2709,7 +2699,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2723,10 +2713,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46111</v>
+        <v>46064</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2739,7 +2729,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2782,7 +2772,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2796,10 +2786,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46111</v>
+        <v>44517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2812,7 +2802,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2855,7 +2845,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2869,10 +2859,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45854</v>
+        <v>44998</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2885,7 +2875,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2928,7 +2918,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2942,10 +2932,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46185</v>
+        <v>46085</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2957,8 +2947,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3001,7 +2996,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45155</v>
+        <v>46106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3030,8 +3025,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>20.9</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44998</v>
+        <v>46111</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44517</v>
+        <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46273</v>
+        <v>44998</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3249,13 +3249,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3298,7 +3293,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3312,10 +3307,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44791</v>
+        <v>45854</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3328,7 +3323,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3371,7 +3366,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3385,10 +3380,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3400,8 +3395,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45155</v>
+        <v>45853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 67005-2021</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>44522</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>1.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45211</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>20.9</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44998</v>
+        <v>45327</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44791</v>
+        <v>46085</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2509,8 +2509,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2553,7 +2558,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2567,10 +2572,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45327</v>
+        <v>46106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2582,8 +2587,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2626,7 +2636,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2640,10 +2650,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46185</v>
+        <v>46111</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2656,7 +2666,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2699,7 +2709,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2713,10 +2723,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46064</v>
+        <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2729,7 +2739,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2772,7 +2782,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2786,10 +2796,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44517</v>
+        <v>45155</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2802,7 +2812,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>20.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2845,7 +2855,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2862,7 +2872,7 @@
         <v>44998</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2875,7 +2885,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2918,7 +2928,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2932,10 +2942,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46085</v>
+        <v>44517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2945,11 +2955,6 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2996,7 +3001,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46106</v>
+        <v>45854</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3025,13 +3030,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46111</v>
+        <v>46064</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46111</v>
+        <v>44791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3237,7 +3237,7 @@
         <v>44998</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45854</v>
+        <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45853</v>
+        <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,275 +1331,275 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>44851</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45211</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44998</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45327</v>
+        <v>45155</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>20.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45119</v>
+        <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46085</v>
+        <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2509,13 +2509,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2558,7 +2553,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2572,10 +2567,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46106</v>
+        <v>44791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2587,13 +2582,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2636,7 +2626,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2650,10 +2640,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46111</v>
+        <v>45327</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2666,7 +2656,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2709,7 +2699,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2723,10 +2713,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2738,8 +2728,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2782,7 +2777,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2796,10 +2791,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45155</v>
+        <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2812,7 +2807,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>20.9</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2855,7 +2850,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2869,10 +2864,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44998</v>
+        <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2885,7 +2880,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2945,7 +2940,7 @@
         <v>44517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3001,7 +2996,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45854</v>
+        <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3031,7 +3026,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3074,7 +3069,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3088,10 +3083,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46064</v>
+        <v>45854</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3104,7 +3099,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3147,7 +3142,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44791</v>
+        <v>46064</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3177,7 +3172,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3220,7 +3215,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3234,10 +3229,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44998</v>
+        <v>46085</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3249,8 +3244,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46273</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44522</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45853</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 47425-2022</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44851</v>
+        <v>46273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1635,17 +1635,22 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1660,59 +1665,60 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gul dropplav
-Strimspindling</t>
+          <t>Bronshjon
+Stubbspretmossa
+Kransmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47425-2022 artfynd.xlsx", "A 47425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 36934-2026 artfynd.xlsx", "A 36934-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47425-2022 karta.png", "A 47425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 36934-2026 karta.png", "A 36934-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47425-2022 georefererad karta.tif", "A 47425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 36934-2026 georefererad karta.tif", "A 36934-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47425-2022 FSC-klagomål.docx", "A 47425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 36934-2026 FSC-klagomål.docx", "A 36934-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47425-2022 FSC-klagomål mail.docx", "A 47425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 36934-2026 FSC-klagomål mail.docx", "A 36934-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47425-2022 tillsynsbegäran.docx", "A 47425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 36934-2026 tillsynsbegäran.docx", "A 36934-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47425-2022 tillsynsbegäran mail.docx", "A 47425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 36934-2026 tillsynsbegäran mail.docx", "A 36934-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23250-2022</t>
+          <t>A 47425-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1722,14 +1728,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44719</v>
+        <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1741,19 +1747,14 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -1762,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1771,10 +1772,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
@@ -1787,43 +1788,43 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Rynkskinn</t>
+          <t>Gul dropplav
+Strimspindling</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 23250-2022 artfynd.xlsx", "A 23250-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47425-2022 artfynd.xlsx", "A 47425-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 23250-2022 karta.png", "A 23250-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47425-2022 karta.png", "A 47425-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 23250-2022 georefererad karta.tif", "A 23250-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47425-2022 georefererad karta.tif", "A 47425-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 23250-2022 FSC-klagomål.docx", "A 23250-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47425-2022 FSC-klagomål.docx", "A 47425-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 23250-2022 FSC-klagomål mail.docx", "A 23250-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47425-2022 FSC-klagomål mail.docx", "A 47425-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 23250-2022 tillsynsbegäran.docx", "A 23250-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47425-2022 tillsynsbegäran.docx", "A 47425-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 23250-2022 tillsynsbegäran mail.docx", "A 23250-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47425-2022 tillsynsbegäran mail.docx", "A 47425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 23250-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1833,14 +1834,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45240</v>
+        <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1852,8 +1853,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1868,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1877,58 +1883,59 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Skogsalm
+Rynkskinn</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 23250-2022 artfynd.xlsx", "A 23250-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 23250-2022 karta.png", "A 23250-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 23250-2022 georefererad karta.tif", "A 23250-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 23250-2022 FSC-klagomål.docx", "A 23250-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 23250-2022 FSC-klagomål mail.docx", "A 23250-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 23250-2022 tillsynsbegäran.docx", "A 23250-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 23250-2022 tillsynsbegäran mail.docx", "A 23250-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1949,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1965,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,46 +2005,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2051,10 +2054,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46273</v>
+        <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2066,13 +2069,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2081,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2096,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2108,67 +2106,67 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37080-2026 artfynd.xlsx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37080-2026 karta.png", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37080-2026 georefererad karta.tif", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37080-2026 FSC-klagomål.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37080-2026 FSC-klagomål mail.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37080-2026 tillsynsbegäran.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37080-2026 tillsynsbegäran mail.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37080-2026 prioriterade fågelarter.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S 3579-2023</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45211</v>
+        <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,11 +2180,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2195,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2213,72 +2211,76 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/S 3579-2023 artfynd.xlsx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37080-2026 artfynd.xlsx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/S 3579-2023 karta.png", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37080-2026 karta.png", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/S 3579-2023 georefererad karta.tif", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37080-2026 georefererad karta.tif", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/S 3579-2023 FSC-klagomål.docx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37080-2026 FSC-klagomål.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/S 3579-2023 FSC-klagomål mail.docx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37080-2026 FSC-klagomål mail.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/S 3579-2023 tillsynsbegäran.docx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37080-2026 tillsynsbegäran.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/S 3579-2023 tillsynsbegäran mail.docx", "S 3579-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37080-2026 tillsynsbegäran mail.docx", "A 37080-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37080-2026 prioriterade fågelarter.docx", "A 37080-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>S 3579-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44998</v>
+        <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,11 +2292,16 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2306,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2315,26 +2322,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/S 3579-2023 artfynd.xlsx", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/S 3579-2023 karta.png", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/S 3579-2023 georefererad karta.tif", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/S 3579-2023 FSC-klagomål.docx", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/S 3579-2023 FSC-klagomål mail.docx", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/S 3579-2023 tillsynsbegäran.docx", "S 3579-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/S 3579-2023 tillsynsbegäran mail.docx", "S 3579-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2348,10 +2387,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2364,7 +2403,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>20.9</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2407,7 +2446,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2421,10 +2460,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44998</v>
+        <v>45155</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2437,7 +2476,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>20.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2480,7 +2519,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2494,10 +2533,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45119</v>
+        <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2510,7 +2549,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2553,7 +2592,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2567,10 +2606,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44791</v>
+        <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2583,7 +2622,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2626,7 +2665,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2640,10 +2679,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45327</v>
+        <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2656,7 +2695,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2699,7 +2738,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2713,10 +2752,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46106</v>
+        <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2728,13 +2767,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2777,7 +2811,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2791,10 +2825,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2806,8 +2840,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2850,7 +2889,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2867,7 +2906,7 @@
         <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2880,7 +2919,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2923,7 +2962,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2937,10 +2976,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44517</v>
+        <v>46111</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2953,7 +2992,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2996,7 +3035,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3010,10 +3049,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44998</v>
+        <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3026,7 +3065,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3069,7 +3108,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3083,10 +3122,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45854</v>
+        <v>44998</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3099,7 +3138,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3142,7 +3181,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3156,10 +3195,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46064</v>
+        <v>45854</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3172,7 +3211,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3215,7 +3254,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3229,10 +3268,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46085</v>
+        <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3244,13 +3283,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3293,7 +3327,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3307,10 +3341,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46185</v>
+        <v>46085</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3322,8 +3356,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3366,7 +3405,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3380,10 +3419,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46273</v>
+        <v>46185</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3395,13 +3434,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45155</v>
+        <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1306,20 +1306,25 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>12.9</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1331,387 +1336,388 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Bronshjon
+Stubbspretmossa
+Kransmossa
+Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 36934-2026 artfynd.xlsx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 36934-2026 karta.png", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 36934-2026 georefererad karta.tif", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 36934-2026 FSC-klagomål.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 36934-2026 FSC-klagomål mail.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 36934-2026 tillsynsbegäran.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 36934-2026 tillsynsbegäran mail.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 36934-2026 prioriterade fågelarter.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 67005-2021</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>44522</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>1.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 35197-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45853</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>0.9</v>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 36934-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Bronshjon
-Stubbspretmossa
-Kransmossa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 36934-2026 artfynd.xlsx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 36934-2026 karta.png", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 36934-2026 georefererad karta.tif", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 36934-2026 FSC-klagomål.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 36934-2026 FSC-klagomål mail.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 36934-2026 tillsynsbegäran.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 36934-2026 tillsynsbegäran mail.docx", "A 36934-2026")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1841,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1958,7 @@
         <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2063,7 @@
         <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2280,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2390,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2463,7 +2469,7 @@
         <v>45155</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2536,7 +2542,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2609,7 +2615,7 @@
         <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2682,7 +2688,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2755,7 +2761,7 @@
         <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2828,7 +2834,7 @@
         <v>46106</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2906,7 +2912,7 @@
         <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2979,7 +2985,7 @@
         <v>46111</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3052,7 +3058,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3125,7 +3131,7 @@
         <v>44998</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3198,7 +3204,7 @@
         <v>45854</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3271,7 +3277,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3344,7 +3350,7 @@
         <v>46085</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3422,7 +3428,7 @@
         <v>46185</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4521-2024</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45327</v>
+        <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,23 +1193,28 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>17.4</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1218,21 +1223,134 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bronshjon
+Stubbspretmossa
+Kransmossa
+Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 36934-2026 artfynd.xlsx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 36934-2026 karta.png", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 36934-2026 georefererad karta.tif", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 36934-2026 FSC-klagomål.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 36934-2026 FSC-klagomål mail.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 36934-2026 tillsynsbegäran.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 36934-2026 tillsynsbegäran mail.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 36934-2026 prioriterade fågelarter.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4521-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Ask
 Fjällig taggsvamp s.str.
@@ -1241,161 +1359,43 @@
 Lönnlav</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 4521-2024 artfynd.xlsx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 4521-2024 karta.png", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 4521-2024 georefererad karta.tif", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 4521-2024 FSC-klagomål.docx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 4521-2024 FSC-klagomål mail.docx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 4521-2024 tillsynsbegäran.docx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 4521-2024 tillsynsbegäran mail.docx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 4521-2024 prioriterade fågelarter.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 36934-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Bronshjon
-Stubbspretmossa
-Kransmossa
-Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 36934-2026 artfynd.xlsx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 36934-2026 karta.png", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 36934-2026 georefererad karta.tif", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 36934-2026 FSC-klagomål.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 36934-2026 FSC-klagomål mail.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 36934-2026 tillsynsbegäran.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 36934-2026 tillsynsbegäran mail.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 36934-2026 prioriterade fågelarter.docx", "A 36934-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1425,19 +1425,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1449,275 +1449,275 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 67005-2021</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>44522</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>1.3</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>2</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>46273</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1970,11 +1970,16 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2007,39 +2012,43 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37080-2026 artfynd.xlsx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37080-2026 karta.png", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37080-2026 georefererad karta.tif", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37080-2026 FSC-klagomål.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37080-2026 FSC-klagomål mail.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37080-2026 tillsynsbegäran.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37080-2026 tillsynsbegäran mail.docx", "A 37080-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37080-2026 prioriterade fågelarter.docx", "A 37080-2026")</f>
         <v/>
       </c>
     </row>
@@ -2063,7 +2072,7 @@
         <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2155,7 +2164,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2169,10 +2178,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46273</v>
+        <v>45240</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2184,16 +2193,11 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2226,43 +2230,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37080-2026 artfynd.xlsx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37080-2026 karta.png", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37080-2026 georefererad karta.tif", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37080-2026 FSC-klagomål.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37080-2026 FSC-klagomål mail.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37080-2026 tillsynsbegäran.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37080-2026 tillsynsbegäran mail.docx", "A 37080-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37080-2026 prioriterade fågelarter.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44998</v>
+        <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>20.9</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44998</v>
+        <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45119</v>
+        <v>45327</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44791</v>
+        <v>46064</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45327</v>
+        <v>46085</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2773,8 +2773,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2834,7 +2839,7 @@
         <v>46106</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2912,7 +2917,7 @@
         <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2985,7 +2990,7 @@
         <v>46111</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3041,7 +3046,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3055,10 +3060,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44517</v>
+        <v>45854</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3071,7 +3076,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3114,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3128,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44998</v>
+        <v>45155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3144,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>20.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3187,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3201,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45854</v>
+        <v>44998</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3217,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3260,7 +3265,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3274,10 +3279,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46064</v>
+        <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3290,7 +3295,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3333,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3347,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46085</v>
+        <v>44791</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3362,13 +3367,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44522</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37080-2026</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46273</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1970,16 +1970,11 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2012,43 +2007,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37080-2026 artfynd.xlsx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37080-2026 karta.png", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37080-2026 georefererad karta.tif", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37080-2026 FSC-klagomål.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37080-2026 FSC-klagomål mail.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37080-2026 tillsynsbegäran.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37080-2026 tillsynsbegäran mail.docx", "A 37080-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37080-2026 prioriterade fågelarter.docx", "A 37080-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2072,7 +2063,7 @@
         <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2155,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37080-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2178,10 +2169,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45240</v>
+        <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2193,11 +2184,16 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2230,39 +2226,43 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37080-2026 artfynd.xlsx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37080-2026 karta.png", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37080-2026 georefererad karta.tif", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37080-2026 FSC-klagomål.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37080-2026 FSC-klagomål mail.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37080-2026 tillsynsbegäran.docx", "A 37080-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37080-2026 tillsynsbegäran mail.docx", "A 37080-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37080-2026 prioriterade fågelarter.docx", "A 37080-2026")</f>
         <v/>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44998</v>
+        <v>46064</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45327</v>
+        <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2627,8 +2627,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2676,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2690,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2700,8 +2705,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2744,7 +2754,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,10 +2768,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46085</v>
+        <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2773,13 +2783,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2822,7 +2827,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2851,13 +2856,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2973,7 +2973,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>20.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45854</v>
+        <v>44791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45155</v>
+        <v>46185</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>20.9</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44998</v>
+        <v>45327</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44791</v>
+        <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3428,7 +3428,7 @@
         <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45853</v>
+        <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1425,19 +1425,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1449,168 +1449,168 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>44522</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2011,42 +2011,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2060,10 +2064,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2076,16 +2080,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2100,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2116,39 +2120,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44998</v>
+        <v>45155</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>20.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46064</v>
+        <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46085</v>
+        <v>45327</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2627,13 +2627,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2676,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2690,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46106</v>
+        <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2705,13 +2700,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2754,7 +2744,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2768,10 +2758,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46111</v>
+        <v>46085</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2783,8 +2773,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2827,7 +2822,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2856,8 +2851,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45854</v>
+        <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2973,7 +2973,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45155</v>
+        <v>46111</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>20.9</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44791</v>
+        <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46185</v>
+        <v>45854</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45327</v>
+        <v>46064</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44517</v>
+        <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44998</v>
+        <v>44791</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3428,7 +3428,7 @@
         <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1425,19 +1425,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1449,168 +1449,168 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>44522</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2011,46 +2011,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2064,10 +2060,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2080,16 +2076,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2104,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2120,35 +2116,39 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45155</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44998</v>
+        <v>46106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2481,8 +2481,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2525,7 +2530,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2544,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45119</v>
+        <v>46111</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2560,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2603,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45327</v>
+        <v>46111</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2628,7 +2633,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2676,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2690,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44998</v>
+        <v>45854</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2701,7 +2706,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2744,7 +2749,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,10 +2763,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46085</v>
+        <v>44998</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2773,13 +2778,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46106</v>
+        <v>45119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2851,13 +2851,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2900,7 +2895,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2914,10 +2909,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46111</v>
+        <v>44791</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2930,7 +2925,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2973,7 +2968,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2987,10 +2982,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46111</v>
+        <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3003,7 +2998,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3063,7 +3058,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3119,7 +3114,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3128,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45854</v>
+        <v>44998</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3144,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3187,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3201,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46064</v>
+        <v>46185</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3217,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3265,7 +3260,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3279,10 +3274,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3295,7 +3290,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3338,7 +3333,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3347,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44791</v>
+        <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3363,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3406,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3425,10 +3420,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44998</v>
+        <v>46085</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3440,8 +3435,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 4521-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46273</v>
+        <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,28 +1193,23 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>17.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1223,21 +1218,139 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Fjällig taggsvamp s.str.
+Talltita
+Bronshjon
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 4521-2024 artfynd.xlsx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 4521-2024 karta.png", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 4521-2024 georefererad karta.tif", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 4521-2024 FSC-klagomål.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 4521-2024 FSC-klagomål mail.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 4521-2024 tillsynsbegäran.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 4521-2024 tillsynsbegäran mail.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 4521-2024 prioriterade fågelarter.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 36934-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>6</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Bronshjon
 Stubbspretmossa
@@ -1246,156 +1359,43 @@
 Tofsmes</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 36934-2026 artfynd.xlsx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 36934-2026 karta.png", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 36934-2026 georefererad karta.tif", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 36934-2026 FSC-klagomål.docx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 36934-2026 FSC-klagomål mail.docx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 36934-2026 tillsynsbegäran.docx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 36934-2026 tillsynsbegäran mail.docx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 36934-2026 prioriterade fågelarter.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 4521-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45327</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Fjällig taggsvamp s.str.
-Talltita
-Bronshjon
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 4521-2024 artfynd.xlsx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 4521-2024 karta.png", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 4521-2024 georefererad karta.tif", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 4521-2024 FSC-klagomål.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 4521-2024 FSC-klagomål mail.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 4521-2024 tillsynsbegäran.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 4521-2024 tillsynsbegäran mail.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 4521-2024 prioriterade fågelarter.docx", "A 4521-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45853</v>
+        <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1425,19 +1425,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1449,275 +1449,275 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2011,42 +2011,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2060,10 +2064,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2076,16 +2080,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2100,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2116,39 +2120,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>20.9</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46106</v>
+        <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2481,13 +2481,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2530,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2544,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46111</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2560,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2603,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2617,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2633,7 +2628,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2676,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2690,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45854</v>
+        <v>45155</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2706,7 +2701,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>20.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2766,7 +2761,7 @@
         <v>44998</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2822,7 +2817,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2836,10 +2831,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45119</v>
+        <v>44517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2852,7 +2847,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2895,7 +2890,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2909,10 +2904,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44791</v>
+        <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2925,7 +2920,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2968,7 +2963,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2982,10 +2977,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45327</v>
+        <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2998,7 +2993,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3041,7 +3036,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3055,10 +3050,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44517</v>
+        <v>46085</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3068,6 +3063,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -3114,7 +3114,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44998</v>
+        <v>44791</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44998</v>
+        <v>46106</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3289,8 +3289,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3333,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3347,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46064</v>
+        <v>46111</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3363,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3406,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3420,10 +3425,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46085</v>
+        <v>46111</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3435,13 +3440,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45155</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44998</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46085</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>44791</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>44998</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>46106</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>46111</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>46111</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45155</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44998</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46085</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>44791</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>44998</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>46106</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>46111</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>46111</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4521-2024</t>
+          <t>A 36934-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45327</v>
+        <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,23 +1193,28 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>17.4</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1218,21 +1223,134 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bronshjon
+Stubbspretmossa
+Kransmossa
+Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 36934-2026 artfynd.xlsx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 36934-2026 karta.png", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 36934-2026 georefererad karta.tif", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 36934-2026 FSC-klagomål.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 36934-2026 FSC-klagomål mail.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 36934-2026 tillsynsbegäran.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 36934-2026 tillsynsbegäran mail.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 36934-2026 prioriterade fågelarter.docx", "A 36934-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4521-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Ask
 Fjällig taggsvamp s.str.
@@ -1241,154 +1359,36 @@
 Lönnlav</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 4521-2024 artfynd.xlsx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 4521-2024 karta.png", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 4521-2024 georefererad karta.tif", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 4521-2024 FSC-klagomål.docx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 4521-2024 FSC-klagomål mail.docx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 4521-2024 tillsynsbegäran.docx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 4521-2024 tillsynsbegäran mail.docx", "A 4521-2024")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 4521-2024 prioriterade fågelarter.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 36934-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Bronshjon
-Stubbspretmossa
-Kransmossa
-Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 36934-2026 artfynd.xlsx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 36934-2026 karta.png", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 36934-2026 georefererad karta.tif", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 36934-2026 FSC-klagomål.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 36934-2026 FSC-klagomål mail.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 36934-2026 tillsynsbegäran.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 36934-2026 tillsynsbegäran mail.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 36934-2026 prioriterade fågelarter.docx", "A 36934-2026")</f>
         <v/>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>44522</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2011,46 +2011,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2064,10 +2060,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2080,16 +2076,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2104,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2120,35 +2116,39 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2396,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45327</v>
+        <v>45155</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>20.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45854</v>
+        <v>46064</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45155</v>
+        <v>46185</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>20.9</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44998</v>
+        <v>44791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2817,7 +2817,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44517</v>
+        <v>46085</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2844,6 +2844,11 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2890,7 +2895,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2904,10 +2909,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46064</v>
+        <v>45327</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2920,7 +2925,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2963,7 +2968,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2977,10 +2982,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46185</v>
+        <v>46106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2992,8 +2997,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3036,7 +3046,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3050,10 +3060,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46085</v>
+        <v>46111</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3065,13 +3075,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3114,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3128,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44791</v>
+        <v>46111</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3144,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3187,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3201,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44998</v>
+        <v>45854</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3217,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3260,7 +3265,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3274,10 +3279,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46106</v>
+        <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3289,13 +3294,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46111</v>
+        <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46111</v>
+        <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 36934-2026</t>
+          <t>A 4521-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46273</v>
+        <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,28 +1193,23 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>17.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1223,21 +1218,139 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Fjällig taggsvamp s.str.
+Talltita
+Bronshjon
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 4521-2024 artfynd.xlsx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 4521-2024 karta.png", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 4521-2024 georefererad karta.tif", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 4521-2024 FSC-klagomål.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 4521-2024 FSC-klagomål mail.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 4521-2024 tillsynsbegäran.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 4521-2024 tillsynsbegäran mail.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 4521-2024 prioriterade fågelarter.docx", "A 4521-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 36934-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>6</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Bronshjon
 Stubbspretmossa
@@ -1246,156 +1359,43 @@
 Tofsmes</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 36934-2026 artfynd.xlsx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 36934-2026 karta.png", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 36934-2026 georefererad karta.tif", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 36934-2026 FSC-klagomål.docx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 36934-2026 FSC-klagomål mail.docx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 36934-2026 tillsynsbegäran.docx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 36934-2026 tillsynsbegäran mail.docx", "A 36934-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 36934-2026 prioriterade fågelarter.docx", "A 36934-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 4521-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45327</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Fjällig taggsvamp s.str.
-Talltita
-Bronshjon
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 4521-2024 artfynd.xlsx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 4521-2024 karta.png", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 4521-2024 georefererad karta.tif", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 4521-2024 FSC-klagomål.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 4521-2024 FSC-klagomål mail.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 4521-2024 tillsynsbegäran.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 4521-2024 tillsynsbegäran mail.docx", "A 4521-2024")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 4521-2024 prioriterade fågelarter.docx", "A 4521-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1425,19 +1425,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1449,275 +1449,275 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 67005-2021</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>44522</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>1.3</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>2</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2011,42 +2011,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2060,10 +2064,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2076,16 +2080,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2100,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2116,39 +2120,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2396,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45155</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>20.9</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v>46064</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46185</v>
+        <v>46085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2700,8 +2700,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2744,7 +2749,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,10 +2763,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44791</v>
+        <v>46106</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2773,8 +2778,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2817,7 +2827,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2831,10 +2841,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46085</v>
+        <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2846,13 +2856,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2895,7 +2900,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2909,10 +2914,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45327</v>
+        <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2925,7 +2930,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2968,7 +2973,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46106</v>
+        <v>45854</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2997,13 +3002,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.6</v>
+        <v>20.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46111</v>
+        <v>44998</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45854</v>
+        <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44517</v>
+        <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44998</v>
+        <v>44791</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3428,7 +3428,7 @@
         <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44522</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2011,46 +2011,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2064,10 +2060,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2080,16 +2076,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2104,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2120,35 +2116,39 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2396,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45327</v>
+        <v>46064</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46064</v>
+        <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2627,8 +2627,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2676,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2690,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2706,7 +2711,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2749,7 +2754,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2763,10 +2768,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2778,13 +2783,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2844,7 +2844,7 @@
         <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2973,7 +2973,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45854</v>
+        <v>45155</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>20.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45155</v>
+        <v>44791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>20.9</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44998</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44517</v>
+        <v>46185</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46185</v>
+        <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44791</v>
+        <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3428,7 +3428,7 @@
         <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 67005-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45853</v>
+        <v>44522</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1425,22 +1425,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1449,275 +1449,275 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 37417-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45155</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>12.9</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2011,42 +2011,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2060,10 +2064,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2076,16 +2080,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2100,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2116,39 +2120,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2396,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46064</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46085</v>
+        <v>44791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2627,13 +2627,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2676,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2690,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46106</v>
+        <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2705,13 +2700,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2754,7 +2744,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2768,10 +2758,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2784,7 +2774,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2827,7 +2817,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2841,10 +2831,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46111</v>
+        <v>46064</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2857,7 +2847,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2900,7 +2890,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2914,10 +2904,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45854</v>
+        <v>46185</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2930,7 +2920,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2973,7 +2963,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2987,10 +2977,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45155</v>
+        <v>46085</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3002,8 +2992,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>20.9</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3046,7 +3041,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3060,10 +3055,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44791</v>
+        <v>46106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3075,8 +3070,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>46111</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46185</v>
+        <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44517</v>
+        <v>45155</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>20.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3355,7 +3355,7 @@
         <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44998</v>
+        <v>44517</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 47653-2024</t>
+          <t>A 16618-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -668,38 +668,38 @@
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 16618-2024</t>
+          <t>A 47653-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45408</v>
+        <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 16618-2024 artfynd.xlsx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 47653-2024 artfynd.xlsx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 16618-2024 karta.png", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 47653-2024 karta.png", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 16618-2024 georefererad karta.tif", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 47653-2024 georefererad karta.tif", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 16618-2024 FSC-klagomål.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 47653-2024 FSC-klagomål.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 16618-2024 FSC-klagomål mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 47653-2024 FSC-klagomål mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 16618-2024 tillsynsbegäran.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 47653-2024 tillsynsbegäran.docx", "A 47653-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 16618-2024 tillsynsbegäran mail.docx", "A 16618-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 47653-2024 tillsynsbegäran mail.docx", "A 47653-2024")</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 67005-2021</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44522</v>
+        <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1425,22 +1425,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1449,275 +1449,275 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2396,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45119</v>
+        <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45327</v>
+        <v>46185</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44791</v>
+        <v>46064</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44998</v>
+        <v>46085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2700,8 +2700,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2744,7 +2749,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,10 +2763,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45854</v>
+        <v>46106</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2773,8 +2778,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2817,7 +2827,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2831,10 +2841,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46064</v>
+        <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2847,7 +2857,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2890,7 +2900,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2904,10 +2914,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46185</v>
+        <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2920,7 +2930,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2963,7 +2973,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46085</v>
+        <v>45854</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2992,13 +3002,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3041,7 +3046,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3055,10 +3060,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46106</v>
+        <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3070,13 +3075,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46111</v>
+        <v>45119</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>20.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45155</v>
+        <v>44791</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>20.9</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44998</v>
+        <v>45327</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
         <v>44517</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44522</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>46185</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>46064</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>46085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>46106</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45854</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45119</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44791</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>45327</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>44517</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44522</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>46185</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>46064</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>46085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>46106</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>46111</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>46111</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45854</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45119</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44791</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>45327</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>44517</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>44522</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44998</v>
+        <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46185</v>
+        <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46064</v>
+        <v>45327</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46085</v>
+        <v>46064</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2700,13 +2700,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2749,7 +2744,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2763,10 +2758,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46106</v>
+        <v>46085</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2784,7 +2779,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2827,7 +2822,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46111</v>
+        <v>45155</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2857,7 +2852,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>20.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2900,7 +2895,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2914,10 +2909,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2929,8 +2924,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2973,7 +2973,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45854</v>
+        <v>46111</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44998</v>
+        <v>46111</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45119</v>
+        <v>44998</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45155</v>
+        <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>20.9</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44791</v>
+        <v>45854</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45327</v>
+        <v>44791</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44517</v>
+        <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 35197-2025</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45853</v>
+        <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1425,19 +1425,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1449,275 +1449,275 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 35197-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45853</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
 Vintertagging</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2011,46 +2011,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2064,10 +2060,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2080,16 +2076,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2104,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2120,35 +2116,39 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44998</v>
+        <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45119</v>
+        <v>45155</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>20.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45327</v>
+        <v>44791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2688,7 +2688,7 @@
         <v>46064</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>46085</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45155</v>
+        <v>45327</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>20.9</v>
+        <v>4.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>46106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>46111</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>46111</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44998</v>
+        <v>44517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44517</v>
+        <v>44998</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>45854</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44791</v>
+        <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44998</v>
+        <v>46185</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37417-2023</t>
+          <t>A 35197-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45155</v>
+        <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1425,19 +1425,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1449,275 +1449,275 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Tallticka
+Vintertagging</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gulvit blekspik
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 37417-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45155</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67005-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44522</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gulvit blekspik
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 35197-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45853</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Tallticka
-Vintertagging</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 35197-2025 artfynd.xlsx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 35197-2025 karta.png", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 35197-2025 georefererad karta.tif", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 35197-2025 FSC-klagomål.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 35197-2025 FSC-klagomål mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 35197-2025 tillsynsbegäran.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 35197-2025 tillsynsbegäran mail.docx", "A 35197-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 35197-2025 prioriterade fågelarter.docx", "A 35197-2025")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55962-2023</t>
+          <t>A 37415-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45240</v>
+        <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2011,42 +2011,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37415-2023</t>
+          <t>A 55962-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2060,10 +2064,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45155</v>
+        <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2076,16 +2080,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2100,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2116,39 +2120,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bolmört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37415-2023 artfynd.xlsx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 55962-2023 artfynd.xlsx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37415-2023 karta.png", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 55962-2023 karta.png", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37415-2023 georefererad karta.tif", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 55962-2023 georefererad karta.tif", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37415-2023 FSC-klagomål.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 55962-2023 FSC-klagomål.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37415-2023 FSC-klagomål mail.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 55962-2023 FSC-klagomål mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37415-2023 tillsynsbegäran.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 55962-2023 tillsynsbegäran.docx", "A 55962-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37415-2023 tillsynsbegäran mail.docx", "A 37415-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/fåglar/A 37415-2023 prioriterade fågelarter.docx", "A 37415-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 55962-2023 tillsynsbegäran mail.docx", "A 55962-2023")</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44998</v>
+        <v>44517</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45119</v>
+        <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45155</v>
+        <v>44791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>20.9</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44791</v>
+        <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46064</v>
+        <v>44998</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46085</v>
+        <v>45327</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2773,13 +2773,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2822,7 +2817,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2836,10 +2831,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45327</v>
+        <v>46185</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2852,7 +2847,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2895,7 +2890,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2909,10 +2904,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46106</v>
+        <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2924,13 +2919,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2973,7 +2963,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2987,10 +2977,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46111</v>
+        <v>46085</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3002,8 +2992,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3046,7 +3041,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3060,10 +3055,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3075,8 +3070,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44517</v>
+        <v>46111</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44998</v>
+        <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>45854</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44998</v>
+        <v>45155</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>20.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>

--- a/Översikt HÅBO.xlsx
+++ b/Översikt HÅBO.xlsx
@@ -601,7 +601,7 @@
         <v>45408</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>45588</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>45595</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44719</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 67005-2021</t>
+          <t>A 37417-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44522</v>
+        <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>12.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1563,161 +1563,161 @@
         <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ullticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 67005-2021</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44522</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÅBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Prakttagging
 Gulvit blekspik
 Lönnlav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 67005-2021 artfynd.xlsx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 67005-2021 karta.png", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 67005-2021 georefererad karta.tif", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 67005-2021 FSC-klagomål.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 67005-2021 FSC-klagomål mail.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 67005-2021 tillsynsbegäran.docx", "A 67005-2021")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 67005-2021 tillsynsbegäran mail.docx", "A 67005-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 37417-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45155</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÅBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Ullticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/artfynd/A 37417-2023 artfynd.xlsx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor/A 37417-2023 karta.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/kartor_geotiff/A 37417-2023 georefererad karta.tif", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/knärot/A 37417-2023 karta knärot.png", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomål/A 37417-2023 FSC-klagomål.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/klagomålsmail/A 37417-2023 FSC-klagomål mail.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsyn/A 37417-2023 tillsynsbegäran.docx", "A 37417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0305/tillsynsmail/A 37417-2023 tillsynsbegäran mail.docx", "A 37417-2023")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44851</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 65836-2021</t>
+          <t>A 12146-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44517</v>
+        <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12146-2023</t>
+          <t>A 32023-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44998</v>
+        <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34202-2022</t>
+          <t>A 4524-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44791</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32023-2023</t>
+          <t>A 8486-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45119</v>
+        <v>46064</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12154-2023</t>
+          <t>A 37410-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44998</v>
+        <v>45155</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.7</v>
+        <v>20.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4524-2024</t>
+          <t>A 11997-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45327</v>
+        <v>46085</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2773,8 +2773,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2817,7 +2822,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27484-2026</t>
+          <t>A 12156-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2831,10 +2836,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46185</v>
+        <v>44998</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2847,7 +2852,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2890,7 +2895,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8486-2026</t>
+          <t>A 15607-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2904,10 +2909,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2919,8 +2924,13 @@
           <t>HÅBO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2963,7 +2973,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11997-2026</t>
+          <t>A 16404-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46085</v>
+        <v>46111</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2992,13 +3002,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3041,7 +3046,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15607-2026</t>
+          <t>A 16325-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3055,10 +3060,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3070,13 +3075,8 @@
           <t>HÅBO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16404-2026</t>
+          <t>A 65836-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46111</v>
+        <v>44517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16325-2026</t>
+          <t>A 35300-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46111</v>
+        <v>45854</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35300-2025</t>
+          <t>A 34202-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45854</v>
+        <v>44791</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37410-2023</t>
+          <t>A 12154-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>20.9</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12156-2023</t>
+          <t>A 27484-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44998</v>
+        <v>46185</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
